--- a/Data/pub_stock.xlsx
+++ b/Data/pub_stock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,131 +452,131 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>241</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AH</t>
+          <t>3BBIF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sSET / SETTHSI</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>668</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>ADVANC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Property &amp; Construction</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SET50 / SETTHSI</t>
+          <t>SET50 / SETHD / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SET100 / SETWB</t>
+          <t>sSET / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121</v>
+        <v>668</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CPF</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Agro &amp; Food Industry</t>
+          <t>Property &amp; Construction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SET50 / SETCLMV / SETHD / SETTHSI / SETWB</t>
+          <t>SET50 / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Property &amp; Construction</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>SET100 / SETWB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IVL</t>
+          <t>CPF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Agro &amp; Food Industry</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SET50 / SETTHSI</t>
+          <t>SET50 / SETCLMV / SETHD / SETTHSI / SETWB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>347</v>
+        <v>127</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORI</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -586,107 +586,367 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SET100 / SETHD / SETTHSI</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>387</v>
+        <v>146</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PTG</t>
+          <t>DIF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Resources</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SET100 / SETHD / SETTHSI</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>443</v>
+        <v>238</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SENA</t>
+          <t>IVL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Property &amp; Construction</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sSET</t>
+          <t>SET50 / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>504</v>
+        <v>245</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SYNEX</t>
+          <t>JMT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SET100 / SETTHSI</t>
+          <t>SET50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>562</v>
+        <v>301</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOA</t>
+          <t>MCS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Property &amp; Construction</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SETTHSI</t>
+          <t>sSET</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>649</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>347</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SET100 / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>387</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SET100 / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>389</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PTT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SET50 / SETCLMV / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>391</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PTTGC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SET50 / SETCLMV / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>401</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RCL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SET100 / SETCLMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>443</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SENA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>452</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SINGER</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SET100</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>489</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SET100 / SETTHSI / SETWB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>504</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SYNEX</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SET100 / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>562</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TOA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>594</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>TVO</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Agro &amp; Food Industry</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>SET / SETTHSI / SETWB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>217</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WHAIR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>630</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WHART</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SET</t>
         </is>
       </c>
     </row>

--- a/Data/pub_stock.xlsx
+++ b/Data/pub_stock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,71 +452,71 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>241</v>
+        <v>11</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3BBIF</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>sSET / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADVANC</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SET50 / SETHD / SETTHSI</t>
+          <t>SET100 / SETWB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AH</t>
+          <t>CPF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Agro &amp; Food Industry</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sSET / SETTHSI</t>
+          <t>SET50 / SETCLMV / SETHD / SETTHSI / SETWB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>668</v>
+        <v>127</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -526,427 +526,167 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SET50 / SETTHSI</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>DIF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SET100 / SETWB</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121</v>
+        <v>238</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CPF</t>
+          <t>IVL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Agro &amp; Food Industry</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SET50 / SETCLMV / SETHD / SETTHSI / SETWB</t>
+          <t>SET50 / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127</v>
+        <v>245</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>JMT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Property &amp; Construction</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>SET50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>146</v>
+        <v>301</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DIF</t>
+          <t>MCS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>sSET</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>238</v>
+        <v>347</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IVL</t>
+          <t>ORI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Property &amp; Construction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SET50 / SETTHSI</t>
+          <t>SET100 / SETHD / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>245</v>
+        <v>389</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JMT</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SET50</t>
+          <t>SET50 / SETCLMV / SETHD / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>301</v>
+        <v>452</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>SINGER</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sSET</t>
+          <t>SET100</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>649</v>
+        <v>562</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>TOA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Agro &amp; Food Industry</t>
+          <t>Property &amp; Construction</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sSET</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>347</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ORI</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Property &amp; Construction</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SET100 / SETHD / SETTHSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>387</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PTG</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Resources</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SET100 / SETHD / SETTHSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>389</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Resources</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SET50 / SETCLMV / SETHD / SETTHSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>391</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PTTGC</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>SET50 / SETCLMV / SETTHSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>401</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>RCL</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SET100 / SETCLMV</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>443</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SENA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Property &amp; Construction</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>sSET</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>452</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SINGER</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>SET100</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>489</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>STA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Agro &amp; Food Industry</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SET100 / SETTHSI / SETWB</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>504</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SYNEX</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>SET100 / SETTHSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>562</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TOA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Property &amp; Construction</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
           <t>SETTHSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>594</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>TVO</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Agro &amp; Food Industry</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>SET / SETTHSI / SETWB</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>217</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>WHAIR</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Property &amp; Construction</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>630</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>WHART</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Property &amp; Construction</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SET</t>
         </is>
       </c>
     </row>

--- a/Data/pub_stock.xlsx
+++ b/Data/pub_stock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,71 +452,71 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>241</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AH</t>
+          <t>3BBIF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sSET / SETTHSI</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>ADVANC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SET100 / SETWB</t>
+          <t>SET50 / SETHD / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CPF</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Agro &amp; Food Industry</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SET50 / SETCLMV / SETHD / SETTHSI / SETWB</t>
+          <t>sSET / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127</v>
+        <v>668</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CPNREIT</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -526,97 +526,97 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>SET50 / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DIF</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>SET100 / SETWB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IVL</t>
+          <t>CPF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Agro &amp; Food Industry</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SET50 / SETTHSI</t>
+          <t>SET50 / SETCLMV / SETHD / SETTHSI / SETWB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>245</v>
+        <v>127</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JMT</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Property &amp; Construction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SET50</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>301</v>
+        <v>146</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>DIF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sSET</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>347</v>
+        <v>209</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORI</t>
+          <t>GVREIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -626,67 +626,367 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SET100 / SETHD / SETTHSI</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>389</v>
+        <v>238</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>IVL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Resources</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SET50 / SETCLMV / SETHD / SETTHSI</t>
+          <t>SET50 / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>452</v>
+        <v>245</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SINGER</t>
+          <t>JMT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SET100</t>
+          <t>SET50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>301</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MCS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>649</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>347</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SET100 / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>387</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SET100 / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>389</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PTT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SET50 / SETCLMV / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>391</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PTTGC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SET50 / SETCLMV / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>401</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RCL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SET100 / SETCLMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>443</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SENA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>452</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SINGER</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SET100</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>489</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SET100 / SETTHSI / SETWB</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>504</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SYNEX</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SET100 / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>655</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TFFIF</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>562</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>TOA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Property &amp; Construction</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>594</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TVO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SET / SETTHSI / SETWB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>217</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WHAIR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>630</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WHART</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SET</t>
         </is>
       </c>
     </row>

--- a/Data/pub_stock.xlsx
+++ b/Data/pub_stock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GVREIT</t>
+          <t>3BBIF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Property &amp; Construction</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -472,19 +472,239 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>655</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TFFIF</t>
+          <t>ADVANC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SET50 / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>sSET / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AIMIRT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>238</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IVL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SET50 / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>245</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JMT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SET50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>301</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MCS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>649</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>391</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PTTGC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SET50 / SETCLMV / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>401</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RCL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SET100 / SETCLMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>452</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SINGER</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SET100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>504</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SYNEX</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SET100 / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>630</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WHART</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>SET</t>
         </is>

--- a/Data/pub_stock.xlsx
+++ b/Data/pub_stock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,16 +532,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>238</v>
+        <v>668</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IVL</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Property &amp; Construction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,159 +552,439 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>245</v>
+        <v>55</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JMT</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SET50</t>
+          <t>SET100 / SETWB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>301</v>
+        <v>121</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MCS</t>
+          <t>CPF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Agro &amp; Food Industry</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sSET</t>
+          <t>SET50 / SETCLMV / SETHD / SETTHSI / SETWB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>649</v>
+        <v>127</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>CPNREIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Agro &amp; Food Industry</t>
+          <t>Property &amp; Construction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sSET</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>391</v>
+        <v>146</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PTTGC</t>
+          <t>DIF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SET50 / SETCLMV / SETTHSI</t>
+          <t>SET</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>401</v>
+        <v>238</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>IVL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SET100 / SETCLMV</t>
+          <t>SET50 / SETTHSI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>452</v>
+        <v>245</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SINGER</t>
+          <t>JMT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SET100</t>
+          <t>SET50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>504</v>
+        <v>301</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SYNEX</t>
+          <t>MCS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SET100 / SETTHSI</t>
+          <t>sSET</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>649</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NER</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>347</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ORI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SET100 / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>750</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PROSPECT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>387</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SET100 / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>389</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PTT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SET50 / SETCLMV / SETHD / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>391</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PTTGC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SET50 / SETCLMV / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>401</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RCL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SET100 / SETCLMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>443</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SENA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sSET</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>452</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SINGER</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SET100</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>489</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SET100 / SETTHSI / SETWB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>504</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SYNEX</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SET100 / SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>562</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TOA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SETTHSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>594</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TVO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Agro &amp; Food Industry</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SET / SETTHSI / SETWB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>217</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WHAIR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>630</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>WHART</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Property &amp; Construction</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>SET</t>
         </is>
